--- a/site/docs/source/Mission-Roster-TNMAN-26.xlsx
+++ b/site/docs/source/Mission-Roster-TNMAN-26.xlsx
@@ -1,18 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93B9CF1-B499-4BDB-BEAB-6C0DC2F21946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="728" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Expected Attachments" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Regimental HQ" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="2nd Battalion" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="3rd Battalion" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="4th Battalion" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Open Items" state="visible" r:id="rId10"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Expected Attachments" sheetId="2" r:id="rId2"/>
+    <sheet name="Regimental HQ" sheetId="3" r:id="rId3"/>
+    <sheet name="2nd Battalion" sheetId="4" r:id="rId4"/>
+    <sheet name="3rd Battalion" sheetId="5" r:id="rId5"/>
+    <sheet name="4th Battalion" sheetId="6" r:id="rId6"/>
+    <sheet name="Open Items" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -127,9 +144,6 @@
     <t>OPFOR at Holston</t>
   </si>
   <si>
-    <t>13-15 MAY. POC Mr. Tony Armstrong. Names TBD.</t>
-  </si>
-  <si>
     <t>Rank</t>
   </si>
   <si>
@@ -869,56 +883,144 @@
   </si>
   <si>
     <t>4BN Feb 2026 PDF lists SGT; regimental Mar 2026 PDF and Sheaf's email list SSG. Using SSG.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13-15 MAY. </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POC Mr. Tony Armstrong. Names TBD.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color rgb="FFF97316"/>
-      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF1B5E20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF5D4037"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFB71C1C"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color rgb="FFF97316"/>
-      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF7C2D12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFB71C1C"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF5D4037"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF1B5E20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFB71C1C"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1006,14 +1108,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1023,44 +1119,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1399,188 +1524,189 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="6" width="10" customWidth="1"/>
+    <col min="1" max="1" width="22" style="8" customWidth="1"/>
+    <col min="2" max="6" width="10" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+    </row>
+    <row r="2" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="9">
         <v>11</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="9">
         <v>5</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="9">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="9">
         <v>0</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="9">
         <v>8</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="9">
         <v>3</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="9">
         <v>3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="9">
         <v>11</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="9">
         <v>6</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="9">
         <v>2</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="9">
         <v>8</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="9">
         <v>3</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>38</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="10">
         <v>17</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="10">
         <v>10</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="10">
         <v>4</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1590,14 +1716,14 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1605,110 +1731,110 @@
     <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+    </row>
+    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
+      <c r="D8" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -1716,14 +1842,14 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1734,307 +1860,307 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="E4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="E5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="15" t="s">
+      <c r="E6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="F11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G12" s="4" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="23" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G12" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2045,250 +2171,250 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="F4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="E8" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G11" s="4" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="23" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G11"/>
+  <autoFilter ref="A3:G11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2299,319 +2425,319 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="F4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="16" t="s">
+      <c r="E10" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="E14" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G14"/>
+  <autoFilter ref="A3:G14" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2622,412 +2748,412 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+    </row>
+    <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="F5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="F6" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="4" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G11"/>
+  <autoFilter ref="A3:G11" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="3" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="4" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="5" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="6" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="7" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="8" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="9" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="10" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="11" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="12" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C12" s="4" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="13" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="14" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>283</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C14"/>
+  <autoFilter ref="A2:C14" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/site/docs/source/Mission-Roster-TNMAN-26.xlsx
+++ b/site/docs/source/Mission-Roster-TNMAN-26.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93B9CF1-B499-4BDB-BEAB-6C0DC2F21946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="728" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="728" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
